--- a/artfynd/A 21341-2026 artfynd.xlsx
+++ b/artfynd/A 21341-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96719837</v>
+        <v>99649286</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>102623</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587282.0937535143</v>
+        <v>587282</v>
       </c>
       <c r="R2" t="n">
-        <v>6421983.472081365</v>
+        <v>6421983</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-18</t>
+          <t>2022-04-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-18</t>
+          <t>2022-04-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +776,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -803,12 +797,7 @@
         <v>96718836</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -852,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587246.2464445042</v>
+        <v>587246</v>
       </c>
       <c r="R3" t="n">
-        <v>6421967.817738037</v>
+        <v>6421968</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,19 +874,9 @@
           <t>2021-10-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96719756</v>
+        <v>96719692</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,7 +934,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587243.9570451608</v>
+        <v>587253</v>
       </c>
       <c r="R4" t="n">
-        <v>6421950.770162569</v>
+        <v>6421997</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,19 +984,9 @@
           <t>2021-10-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,15 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96719779</v>
+        <v>96719709</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1044,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1102,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587282.1400571048</v>
+        <v>587246</v>
       </c>
       <c r="R5" t="n">
-        <v>6421981.348392073</v>
+        <v>6421970</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,19 +1094,9 @@
           <t>2021-10-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,15 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96719692</v>
+        <v>96719756</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1227,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587253.0570401822</v>
+        <v>587244</v>
       </c>
       <c r="R6" t="n">
-        <v>6421997.180773203</v>
+        <v>6421951</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1260,19 +1204,9 @@
           <t>2021-10-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,15 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96719709</v>
+        <v>96719779</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1264,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1352,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587245.6682274094</v>
+        <v>587282</v>
       </c>
       <c r="R7" t="n">
-        <v>6421969.929841251</v>
+        <v>6421981</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1385,19 +1314,9 @@
           <t>2021-10-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,6 +1341,116 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96719837</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Södersjö, Lofta, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>587282</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6421983</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-10-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-10-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
